--- a/TEST-DATA/Структура таблиц НСИ F___ — копия.xlsx
+++ b/TEST-DATA/Структура таблиц НСИ F___ — копия.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="75" windowWidth="28755" windowHeight="12600" tabRatio="916" firstSheet="15" activeTab="18"/>
+    <workbookView xWindow="0" yWindow="75" windowWidth="28755" windowHeight="12600" tabRatio="916" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="f001_tfoms" sheetId="1" r:id="rId1"/>
@@ -764,7 +764,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -787,6 +787,7 @@
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -5846,622 +5847,731 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
+    <row r="1" spans="1:12">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="21" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2">
+      <c r="C2" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="21">
         <v>5</v>
       </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="E2" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="21"/>
+      <c r="L2" s="22"/>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3">
+      <c r="C3" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="21">
         <v>5</v>
       </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="E3" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" s="21"/>
+      <c r="L3" s="22"/>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4">
+      <c r="C4" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="21">
         <v>254</v>
       </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="E4" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" s="21"/>
+      <c r="L4" s="22"/>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5">
+      <c r="C5" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="21">
         <v>250</v>
       </c>
-      <c r="E5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="E5" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="K5" s="21"/>
+      <c r="L5" s="22"/>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="C6" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="21">
+        <v>12</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="K6" s="21"/>
+      <c r="L6" s="22"/>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7">
+      <c r="C7" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="21">
         <v>15</v>
       </c>
-      <c r="E7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="E7" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="K7" s="21"/>
+      <c r="L7" s="22"/>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8">
+      <c r="C8" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="21">
         <v>9</v>
       </c>
-      <c r="E8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="E8" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" s="21"/>
+      <c r="L8" s="22"/>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9">
+      <c r="C9" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="21">
         <v>6</v>
       </c>
-      <c r="E9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" t="s">
-        <v>12</v>
-      </c>
-      <c r="I9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+      <c r="E9" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" s="21"/>
+      <c r="L9" s="22"/>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10">
+      <c r="C10" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="21">
         <v>254</v>
       </c>
-      <c r="E10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" t="s">
-        <v>12</v>
-      </c>
-      <c r="I10" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+      <c r="E10" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="K10" s="21"/>
+      <c r="L10" s="22"/>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11">
+      <c r="C11" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="21">
         <v>6</v>
       </c>
-      <c r="E11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I11" t="s">
-        <v>20</v>
-      </c>
-      <c r="J11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="E11" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="K11" s="21"/>
+      <c r="L11" s="22"/>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12">
+      <c r="C12" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="21">
         <v>254</v>
       </c>
-      <c r="E12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" t="s">
-        <v>12</v>
-      </c>
-      <c r="I12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+      <c r="E12" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I12" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="K12" s="21"/>
+      <c r="L12" s="22"/>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13">
+      <c r="C13" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="21">
         <v>5</v>
       </c>
-      <c r="E13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H13" t="s">
-        <v>12</v>
-      </c>
-      <c r="I13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="E13" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13" s="21"/>
+      <c r="L13" s="22"/>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14">
+      <c r="C14" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="21">
         <v>40</v>
       </c>
-      <c r="E14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" t="s">
-        <v>12</v>
-      </c>
-      <c r="I14" t="s">
-        <v>20</v>
-      </c>
-      <c r="J14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="E14" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I14" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="K14" s="21"/>
+      <c r="L14" s="22"/>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15">
+      <c r="C15" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="21">
         <v>40</v>
       </c>
-      <c r="E15" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" t="s">
-        <v>12</v>
-      </c>
-      <c r="I15" t="s">
-        <v>20</v>
-      </c>
-      <c r="J15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+      <c r="E15" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I15" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="K15" s="21"/>
+      <c r="L15" s="22"/>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C16" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16">
+      <c r="C16" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="21">
         <v>40</v>
       </c>
-      <c r="E16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" t="s">
-        <v>20</v>
-      </c>
-      <c r="H16" t="s">
-        <v>12</v>
-      </c>
-      <c r="I16" t="s">
-        <v>20</v>
-      </c>
-      <c r="J16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+      <c r="E16" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I16" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="K16" s="21"/>
+      <c r="L16" s="22"/>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C17" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17">
+      <c r="C17" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="21">
         <v>100</v>
       </c>
-      <c r="E17" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17" t="s">
-        <v>12</v>
-      </c>
-      <c r="I17" t="s">
-        <v>20</v>
-      </c>
-      <c r="J17" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+      <c r="E17" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I17" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="K17" s="21"/>
+      <c r="L17" s="22"/>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="C18" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18">
+      <c r="C18" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="21">
         <v>5</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="21">
         <v>1</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="21">
         <v>0</v>
       </c>
-      <c r="G18" t="s">
-        <v>20</v>
-      </c>
-      <c r="H18" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J18" t="s">
+      <c r="G18" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="21" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="19" spans="1:10">
+      <c r="K18" s="21"/>
+      <c r="L18" s="22"/>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C19" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19">
+      <c r="C19" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="21">
         <v>40</v>
       </c>
-      <c r="E19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" t="s">
-        <v>20</v>
-      </c>
-      <c r="H19" t="s">
-        <v>12</v>
-      </c>
-      <c r="I19" t="s">
-        <v>20</v>
-      </c>
-      <c r="J19" t="s">
-        <v>14</v>
-      </c>
+      <c r="E19" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I19" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="K19" s="21"/>
+      <c r="L19" s="22"/>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="22"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="22"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="22"/>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="22"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="22"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="22"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="22"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/TEST-DATA/Структура таблиц НСИ F___ — копия.xlsx
+++ b/TEST-DATA/Структура таблиц НСИ F___ — копия.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="75" windowWidth="28755" windowHeight="12600" tabRatio="916" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="75" windowWidth="28755" windowHeight="12600" tabRatio="916" firstSheet="4" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="f001_tfoms" sheetId="1" r:id="rId1"/>
@@ -618,7 +618,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -751,6 +751,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -764,7 +770,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -788,6 +794,7 @@
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2355,7 +2362,7 @@
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="23" t="s">
         <v>96</v>
       </c>
       <c r="B2" t="s">

--- a/TEST-DATA/Структура таблиц НСИ F___ — копия.xlsx
+++ b/TEST-DATA/Структура таблиц НСИ F___ — копия.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="75" windowWidth="28755" windowHeight="12600" tabRatio="916" firstSheet="4" activeTab="10"/>
+    <workbookView xWindow="0" yWindow="75" windowWidth="28755" windowHeight="12600" tabRatio="916" firstSheet="6" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="f001_tfoms" sheetId="1" r:id="rId1"/>
@@ -618,7 +618,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -711,12 +711,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF8367A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF6C6D8A"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -770,7 +764,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -787,14 +781,13 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2188,7 +2181,7 @@
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>94</v>
       </c>
       <c r="B2" t="s">
@@ -2220,7 +2213,7 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="15" t="s">
         <v>95</v>
       </c>
       <c r="B3" t="s">
@@ -2252,7 +2245,7 @@
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="15" t="s">
         <v>86</v>
       </c>
       <c r="B4" s="10" t="s">
@@ -2284,7 +2277,7 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="15" t="s">
         <v>87</v>
       </c>
       <c r="B5" s="10" t="s">
@@ -2362,7 +2355,7 @@
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="22" t="s">
         <v>96</v>
       </c>
       <c r="B2" t="s">
@@ -2596,7 +2589,7 @@
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="22" t="s">
         <v>100</v>
       </c>
       <c r="B2" t="s">
@@ -2628,7 +2621,7 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="22" t="s">
         <v>101</v>
       </c>
       <c r="B3" t="s">
@@ -2660,7 +2653,7 @@
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="22" t="s">
         <v>102</v>
       </c>
       <c r="B4" t="s">
@@ -2692,7 +2685,7 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="22" t="s">
         <v>103</v>
       </c>
       <c r="B5" t="s">
@@ -2797,6 +2790,7 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4475,7 +4469,7 @@
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="17" t="s">
         <v>134</v>
       </c>
       <c r="B8" t="s">
@@ -4507,7 +4501,7 @@
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="17" t="s">
         <v>135</v>
       </c>
       <c r="B9" t="s">
@@ -4539,7 +4533,7 @@
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="17" t="s">
         <v>136</v>
       </c>
       <c r="B10" t="s">
@@ -4916,7 +4910,7 @@
       <c r="L2" s="11"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="17" t="s">
         <v>128</v>
       </c>
       <c r="B3" t="s">
@@ -5205,7 +5199,7 @@
       <c r="K11" s="11"/>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="17" t="s">
         <v>148</v>
       </c>
       <c r="B12" t="s">
@@ -5271,7 +5265,7 @@
       <c r="L13" s="11"/>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="19" t="s">
         <v>150</v>
       </c>
       <c r="B14" t="s">
@@ -5303,7 +5297,7 @@
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="19" t="s">
         <v>134</v>
       </c>
       <c r="B15" t="s">
@@ -5335,7 +5329,7 @@
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="19" t="s">
         <v>151</v>
       </c>
       <c r="B16" t="s">
@@ -5367,7 +5361,7 @@
       </c>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="19" t="s">
         <v>129</v>
       </c>
       <c r="B17" t="s">
@@ -5399,7 +5393,7 @@
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="19" t="s">
         <v>131</v>
       </c>
       <c r="B18" t="s">
@@ -5623,7 +5617,7 @@
       </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="17" t="s">
         <v>136</v>
       </c>
       <c r="B25" t="s">
@@ -5861,720 +5855,720 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="H1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="I1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="J1" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="21">
+      <c r="C2" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="20">
         <v>5</v>
       </c>
-      <c r="E2" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="21"/>
-      <c r="L2" s="22"/>
+      <c r="E2" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="20"/>
+      <c r="L2" s="21"/>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="21">
+      <c r="C3" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="20">
         <v>5</v>
       </c>
-      <c r="E3" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="K3" s="21"/>
-      <c r="L3" s="22"/>
+      <c r="E3" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" s="20"/>
+      <c r="L3" s="21"/>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="21">
+      <c r="C4" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="20">
         <v>254</v>
       </c>
-      <c r="E4" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="K4" s="21"/>
-      <c r="L4" s="22"/>
+      <c r="E4" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" s="20"/>
+      <c r="L4" s="21"/>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="21">
+      <c r="C5" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="20">
         <v>250</v>
       </c>
-      <c r="E5" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" s="21"/>
-      <c r="L5" s="22"/>
+      <c r="E5" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K5" s="20"/>
+      <c r="L5" s="21"/>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="21">
-        <v>12</v>
-      </c>
-      <c r="E6" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="K6" s="21"/>
-      <c r="L6" s="22"/>
+      <c r="C6" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="20">
+        <v>12</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K6" s="20"/>
+      <c r="L6" s="21"/>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="21">
+      <c r="C7" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="20">
         <v>15</v>
       </c>
-      <c r="E7" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="J7" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="K7" s="21"/>
-      <c r="L7" s="22"/>
+      <c r="E7" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K7" s="20"/>
+      <c r="L7" s="21"/>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="21">
+      <c r="C8" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="20">
         <v>9</v>
       </c>
-      <c r="E8" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="J8" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" s="21"/>
-      <c r="L8" s="22"/>
+      <c r="E8" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" s="20"/>
+      <c r="L8" s="21"/>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="21">
+      <c r="C9" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="20">
         <v>6</v>
       </c>
-      <c r="E9" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="I9" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="J9" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="21"/>
-      <c r="L9" s="22"/>
+      <c r="E9" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" s="20"/>
+      <c r="L9" s="21"/>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="21">
+      <c r="C10" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="20">
         <v>254</v>
       </c>
-      <c r="E10" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="I10" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="K10" s="21"/>
-      <c r="L10" s="22"/>
+      <c r="E10" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K10" s="20"/>
+      <c r="L10" s="21"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="21">
+      <c r="C11" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="20">
         <v>6</v>
       </c>
-      <c r="E11" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="I11" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="J11" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="K11" s="21"/>
-      <c r="L11" s="22"/>
+      <c r="E11" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K11" s="20"/>
+      <c r="L11" s="21"/>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="21">
+      <c r="C12" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="20">
         <v>254</v>
       </c>
-      <c r="E12" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="I12" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="J12" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="K12" s="21"/>
-      <c r="L12" s="22"/>
+      <c r="E12" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="I12" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K12" s="20"/>
+      <c r="L12" s="21"/>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="21">
+      <c r="C13" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="20">
         <v>5</v>
       </c>
-      <c r="E13" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="H13" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="I13" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="J13" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" s="21"/>
-      <c r="L13" s="22"/>
+      <c r="E13" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13" s="20"/>
+      <c r="L13" s="21"/>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="21">
+      <c r="C14" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="20">
         <v>40</v>
       </c>
-      <c r="E14" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="I14" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="J14" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="K14" s="21"/>
-      <c r="L14" s="22"/>
+      <c r="E14" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="I14" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K14" s="20"/>
+      <c r="L14" s="21"/>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="21">
+      <c r="C15" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="20">
         <v>40</v>
       </c>
-      <c r="E15" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="I15" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="J15" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="K15" s="21"/>
-      <c r="L15" s="22"/>
+      <c r="E15" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="I15" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K15" s="20"/>
+      <c r="L15" s="21"/>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="21">
+      <c r="C16" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="20">
         <v>40</v>
       </c>
-      <c r="E16" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="H16" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="I16" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="J16" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="K16" s="21"/>
-      <c r="L16" s="22"/>
+      <c r="E16" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="I16" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K16" s="20"/>
+      <c r="L16" s="21"/>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="21">
+      <c r="C17" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="20">
         <v>100</v>
       </c>
-      <c r="E17" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="I17" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="J17" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="K17" s="21"/>
-      <c r="L17" s="22"/>
+      <c r="E17" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="I17" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K17" s="20"/>
+      <c r="L17" s="21"/>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="21">
+      <c r="C18" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="20">
         <v>5</v>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="20">
         <v>1</v>
       </c>
-      <c r="F18" s="21">
+      <c r="F18" s="20">
         <v>0</v>
       </c>
-      <c r="G18" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="H18" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="J18" s="21" t="s">
+      <c r="G18" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="K18" s="21"/>
-      <c r="L18" s="22"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="21"/>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="21">
+      <c r="C19" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="20">
         <v>40</v>
       </c>
-      <c r="E19" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="H19" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="I19" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="J19" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="K19" s="21"/>
-      <c r="L19" s="22"/>
+      <c r="E19" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="I19" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K19" s="20"/>
+      <c r="L19" s="21"/>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="22"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="22"/>
-      <c r="L20" s="22"/>
+      <c r="A20" s="21"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="21"/>
+      <c r="L20" s="21"/>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="22"/>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
-      <c r="J21" s="22"/>
-      <c r="K21" s="22"/>
-      <c r="L21" s="22"/>
+      <c r="A21" s="21"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="21"/>
+      <c r="K21" s="21"/>
+      <c r="L21" s="21"/>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="22"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
+      <c r="A22" s="21"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="21"/>
+      <c r="L22" s="21"/>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="22"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22"/>
+      <c r="A23" s="21"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="21"/>
+      <c r="K23" s="21"/>
+      <c r="L23" s="21"/>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="22"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="22"/>
-      <c r="K24" s="22"/>
-      <c r="L24" s="22"/>
+      <c r="A24" s="21"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="21"/>
+      <c r="L24" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6759,7 +6753,7 @@
       <c r="L5" s="11"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="16" t="s">
         <v>141</v>
       </c>
       <c r="B6" t="s">
@@ -6791,7 +6785,7 @@
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>147</v>
       </c>
       <c r="B7" t="s">
@@ -7000,7 +6994,7 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>156</v>
       </c>
       <c r="B2" t="s">
@@ -7035,7 +7029,7 @@
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="17" t="s">
         <v>161</v>
       </c>
       <c r="B3" t="s">
@@ -7070,106 +7064,106 @@
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="C4" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="21">
+      <c r="C4" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="20">
         <v>4</v>
       </c>
-      <c r="E4" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="J4" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
+      <c r="E4" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="21">
+      <c r="C5" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="20">
         <v>2</v>
       </c>
-      <c r="E5" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="J5" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" s="21"/>
-      <c r="L5" s="21"/>
+      <c r="E5" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="C6" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="21">
+      <c r="C6" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="20">
         <v>3</v>
       </c>
-      <c r="E6" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="J6" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="K6" s="21"/>
-      <c r="L6" s="21"/>
+      <c r="E6" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="11" t="s">
@@ -7279,7 +7273,7 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>165</v>
       </c>
       <c r="B2" t="s">
@@ -7311,7 +7305,7 @@
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>134</v>
       </c>
       <c r="B3" t="s">
@@ -7378,7 +7372,7 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>167</v>
       </c>
       <c r="B5" t="s">
@@ -7413,7 +7407,7 @@
       </c>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>168</v>
       </c>
       <c r="B6" t="s">
@@ -7589,7 +7583,7 @@
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="17" t="s">
         <v>167</v>
       </c>
       <c r="B3" t="s">
@@ -7624,7 +7618,7 @@
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="17" t="s">
         <v>156</v>
       </c>
       <c r="B4" t="s">

--- a/TEST-DATA/Структура таблиц НСИ F___ — копия.xlsx
+++ b/TEST-DATA/Структура таблиц НСИ F___ — копия.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="75" windowWidth="28755" windowHeight="12600" tabRatio="916" firstSheet="6" activeTab="12"/>
+    <workbookView xWindow="0" yWindow="75" windowWidth="28755" windowHeight="12600" tabRatio="916" firstSheet="12" activeTab="16"/>
   </bookViews>
   <sheets>
     <sheet name="f001_tfoms" sheetId="1" r:id="rId1"/>
@@ -618,7 +618,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -751,6 +751,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -764,7 +770,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -788,6 +794,7 @@
     <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -4090,7 +4097,7 @@
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="23" t="s">
         <v>10</v>
       </c>
       <c r="B7" t="s">
@@ -4122,7 +4129,7 @@
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="23" t="s">
         <v>50</v>
       </c>
       <c r="B8" t="s">
